--- a/data/trans_dic/IP74A1_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP74A1_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que han resulto los pagos de la hipoteca</t>
+          <t>Adulto que han resulto los pagos de la hipoteca (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Primarios</t>
+          <t>Secundarios</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -548,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>61,88; 100,0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,24; 100,0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Secundarios</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -598,7 +599,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -608,7 +609,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>59,24; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,51; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,51; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Universitarios</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -648,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>93,74%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,246 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>67,51; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100</t>
+          <t>86,13; 100,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A6:A7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que han resulto los pagos de la hipoteca (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5605</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8842</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14447</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3744; 6050</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12694; 14892</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1057</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2806</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3863</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -693,22 +923,22 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
+          <t>n</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -716,39 +946,61 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6662</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11648</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18311</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
           <t>IC 95%</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>65,47; 100,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>90,01; 100</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>87,62; 100,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4798; 7107</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16155; 18756</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+  <mergeCells count="4">
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A4:A6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
